--- a/Courses/Term 3/QAM-III/Case Studies/925 DATA - with USA MAP - Gravity.xlsx
+++ b/Courses/Term 3/QAM-III/Case Studies/925 DATA - with USA MAP - Gravity.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="11028"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29426"/>
   <workbookPr autoCompressPictures="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/suranjandas/Desktop/SIRMAUR. IIM .. Nov 14 2025/T1 - Non Linear Programming/Data to students/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\MBA\Courses\Term 3\QAM-III\Case Studies\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{69B6A47B-CF9F-E14C-BD43-18A841FD1428}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E5E68D70-3E00-420A-931D-F0A4E0709756}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="740" windowWidth="29400" windowHeight="17240" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="DATA" sheetId="1" r:id="rId1"/>
@@ -21,10 +21,11 @@
     <sheet name="Sheet6" sheetId="6" r:id="rId6"/>
   </sheets>
   <definedNames>
-    <definedName name="solver_adj" localSheetId="0" hidden="1">DATA!$E$14:$F$14</definedName>
+    <definedName name="solver_adj" localSheetId="0" hidden="1">DATA!$E$38:$F$38</definedName>
     <definedName name="solver_cvg" localSheetId="0" hidden="1">0.0001</definedName>
     <definedName name="solver_drv" localSheetId="0" hidden="1">1</definedName>
     <definedName name="solver_eng" localSheetId="0" hidden="1">1</definedName>
+    <definedName name="solver_est" localSheetId="0" hidden="1">1</definedName>
     <definedName name="solver_itr" localSheetId="0" hidden="1">2147483647</definedName>
     <definedName name="solver_lin" localSheetId="0" hidden="1">2</definedName>
     <definedName name="solver_mip" localSheetId="0" hidden="1">2147483647</definedName>
@@ -34,7 +35,8 @@
     <definedName name="solver_neg" localSheetId="0" hidden="1">1</definedName>
     <definedName name="solver_nod" localSheetId="0" hidden="1">2147483647</definedName>
     <definedName name="solver_num" localSheetId="0" hidden="1">0</definedName>
-    <definedName name="solver_opt" localSheetId="0" hidden="1">DATA!$K$15</definedName>
+    <definedName name="solver_nwt" localSheetId="0" hidden="1">1</definedName>
+    <definedName name="solver_opt" localSheetId="0" hidden="1">DATA!$H$36</definedName>
     <definedName name="solver_pre" localSheetId="0" hidden="1">0.000001</definedName>
     <definedName name="solver_rbv" localSheetId="0" hidden="1">1</definedName>
     <definedName name="solver_rlx" localSheetId="0" hidden="1">1</definedName>
@@ -46,7 +48,7 @@
     <definedName name="solver_tol" localSheetId="0" hidden="1">0.01</definedName>
     <definedName name="solver_typ" localSheetId="0" hidden="1">2</definedName>
     <definedName name="solver_val" localSheetId="0" hidden="1">0</definedName>
-    <definedName name="solver_ver" localSheetId="0" hidden="1">2</definedName>
+    <definedName name="solver_ver" localSheetId="0" hidden="1">3</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -68,7 +70,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="20">
   <si>
     <t>Seattle</t>
   </si>
@@ -113,6 +115,21 @@
   </si>
   <si>
     <t>Source : 200RS6</t>
+  </si>
+  <si>
+    <t>x</t>
+  </si>
+  <si>
+    <t>y</t>
+  </si>
+  <si>
+    <t>DEVIATION VARIABLES</t>
+  </si>
+  <si>
+    <t>DISTANCE SQRT</t>
+  </si>
+  <si>
+    <t>DEMAND</t>
   </si>
 </sst>
 </file>
@@ -264,11 +281,11 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="17">
@@ -367,7 +384,7 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>13</xdr:col>
-      <xdr:colOff>479581</xdr:colOff>
+      <xdr:colOff>153009</xdr:colOff>
       <xdr:row>21</xdr:row>
       <xdr:rowOff>174859</xdr:rowOff>
     </xdr:to>
@@ -1237,37 +1254,37 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:AB173"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="3" max="3" width="15.6640625" customWidth="1"/>
     <col min="4" max="4" width="19" customWidth="1"/>
-    <col min="5" max="5" width="17.5" customWidth="1"/>
+    <col min="5" max="5" width="17.44140625" customWidth="1"/>
     <col min="6" max="6" width="16.6640625" customWidth="1"/>
-    <col min="7" max="7" width="9.33203125" customWidth="1"/>
+    <col min="7" max="7" width="14.109375" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="10.6640625" customWidth="1"/>
-    <col min="9" max="9" width="9.5" customWidth="1"/>
+    <col min="9" max="9" width="9.44140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:28" ht="37" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="14" t="s">
+    <row r="1" spans="1:28" ht="37.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="15" t="s">
         <v>8</v>
       </c>
-      <c r="B1" s="14"/>
-      <c r="C1" s="14"/>
-      <c r="D1" s="14"/>
-      <c r="E1" s="14"/>
-      <c r="F1" s="14"/>
-      <c r="G1" s="14"/>
-    </row>
-    <row r="3" spans="1:28" ht="32" x14ac:dyDescent="0.2">
+      <c r="B1" s="15"/>
+      <c r="C1" s="15"/>
+      <c r="D1" s="15"/>
+      <c r="E1" s="15"/>
+      <c r="F1" s="15"/>
+      <c r="G1" s="15"/>
+    </row>
+    <row r="3" spans="1:28" ht="43.2" x14ac:dyDescent="0.3">
       <c r="C3" s="13" t="s">
         <v>12</v>
       </c>
-      <c r="D3" s="15" t="s">
+      <c r="D3" s="14" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="4" spans="1:28" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:28" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="I4" s="8"/>
       <c r="J4" s="8"/>
       <c r="K4" s="8"/>
@@ -1275,9 +1292,13 @@
       <c r="M4" s="8"/>
       <c r="N4" s="8"/>
     </row>
-    <row r="5" spans="1:28" ht="16" x14ac:dyDescent="0.2">
-      <c r="E5" s="6"/>
-      <c r="F5" s="6"/>
+    <row r="5" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="E5" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="F5" s="6" t="s">
+        <v>16</v>
+      </c>
       <c r="H5" s="8"/>
       <c r="K5" s="8"/>
       <c r="L5" s="8" t="str">
@@ -1296,7 +1317,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="6" spans="1:28" ht="16" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:28" x14ac:dyDescent="0.3">
       <c r="C6" s="7" t="s">
         <v>0</v>
       </c>
@@ -1323,7 +1344,7 @@
         <v>122.33</v>
       </c>
     </row>
-    <row r="7" spans="1:28" ht="16" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:28" x14ac:dyDescent="0.3">
       <c r="C7" s="7" t="s">
         <v>1</v>
       </c>
@@ -1350,7 +1371,7 @@
         <v>122.42</v>
       </c>
     </row>
-    <row r="8" spans="1:28" ht="16" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:28" x14ac:dyDescent="0.3">
       <c r="C8" s="7" t="s">
         <v>2</v>
       </c>
@@ -1377,7 +1398,7 @@
         <v>117.16</v>
       </c>
     </row>
-    <row r="9" spans="1:28" ht="16" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:28" x14ac:dyDescent="0.3">
       <c r="C9" s="7" t="s">
         <v>3</v>
       </c>
@@ -1404,7 +1425,7 @@
         <v>81.3</v>
       </c>
     </row>
-    <row r="10" spans="1:28" ht="16" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:28" x14ac:dyDescent="0.3">
       <c r="C10" s="7" t="s">
         <v>4</v>
       </c>
@@ -1431,7 +1452,7 @@
         <v>95.38</v>
       </c>
     </row>
-    <row r="11" spans="1:28" ht="16" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:28" x14ac:dyDescent="0.3">
       <c r="C11" s="7" t="s">
         <v>5</v>
       </c>
@@ -1456,7 +1477,7 @@
         <v>71.06</v>
       </c>
     </row>
-    <row r="12" spans="1:28" ht="16" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:28" x14ac:dyDescent="0.3">
       <c r="C12" s="7" t="s">
         <v>6</v>
       </c>
@@ -1481,7 +1502,7 @@
         <v>87.68</v>
       </c>
     </row>
-    <row r="13" spans="1:28" ht="16" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:28" x14ac:dyDescent="0.3">
       <c r="C13" s="7" t="s">
         <v>7</v>
       </c>
@@ -1505,98 +1526,250 @@
         <v>93.27</v>
       </c>
     </row>
-    <row r="14" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:28" x14ac:dyDescent="0.3">
       <c r="C14" s="1"/>
       <c r="E14" s="4"/>
       <c r="F14" s="4"/>
     </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="27" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="C25" s="12" t="s">
+        <v>11</v>
+      </c>
+      <c r="D25" s="10"/>
+      <c r="E25" s="10"/>
+      <c r="F25" s="10"/>
+    </row>
+    <row r="26" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="C26" s="10"/>
+      <c r="D26" s="10"/>
+      <c r="E26" s="10"/>
+      <c r="F26" s="10"/>
+    </row>
+    <row r="27" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B27" s="2"/>
-    </row>
-    <row r="28" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="C27" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="D27" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="E27" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="F27" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="G27" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="H27" s="10" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="28" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B28" s="10"/>
-      <c r="E28" s="10"/>
-      <c r="F28" s="10"/>
-      <c r="G28" s="10"/>
-      <c r="H28" s="10"/>
+      <c r="C28" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="D28" s="2">
+        <v>50</v>
+      </c>
+      <c r="E28" s="11">
+        <v>47.61</v>
+      </c>
+      <c r="F28" s="11">
+        <v>122.33</v>
+      </c>
+      <c r="G28" s="10">
+        <f>SQRT(SUMXMY2(E28:F28,$E$38:$F$38))</f>
+        <v>34.135425776395117</v>
+      </c>
+      <c r="H28" s="10">
+        <f>G28*D28</f>
+        <v>1706.7712888197559</v>
+      </c>
       <c r="I28" s="10"/>
     </row>
-    <row r="29" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B29" s="10"/>
-      <c r="E29" s="10"/>
-      <c r="F29" s="10"/>
-      <c r="G29" s="10"/>
-      <c r="H29" s="10"/>
+      <c r="C29" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="D29" s="2">
+        <v>180</v>
+      </c>
+      <c r="E29" s="11">
+        <v>37.78</v>
+      </c>
+      <c r="F29" s="11">
+        <v>122.42</v>
+      </c>
+      <c r="G29" s="10">
+        <f t="shared" ref="G29:G35" si="2">SQRT(SUMXMY2(E29:F29,$E$38:$F$38))</f>
+        <v>33.667953813686928</v>
+      </c>
+      <c r="H29" s="10">
+        <f t="shared" ref="H29:H35" si="3">G29*D29</f>
+        <v>6060.2316864636468</v>
+      </c>
       <c r="I29" s="10"/>
     </row>
-    <row r="30" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A30" s="10"/>
       <c r="B30" s="10"/>
-      <c r="E30" s="10"/>
-      <c r="F30" s="10"/>
-      <c r="G30" s="10"/>
-      <c r="H30" s="10"/>
+      <c r="C30" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="D30" s="2">
+        <v>80</v>
+      </c>
+      <c r="E30" s="11">
+        <v>32.72</v>
+      </c>
+      <c r="F30" s="11">
+        <v>117.16</v>
+      </c>
+      <c r="G30" s="10">
+        <f t="shared" si="2"/>
+        <v>29.399692630286644</v>
+      </c>
+      <c r="H30" s="10">
+        <f t="shared" si="3"/>
+        <v>2351.9754104229314</v>
+      </c>
       <c r="I30" s="10"/>
     </row>
-    <row r="31" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A31" s="10"/>
       <c r="B31" s="10"/>
-      <c r="E31" s="10"/>
-      <c r="F31" s="10"/>
-      <c r="G31" s="10"/>
-      <c r="H31" s="10"/>
+      <c r="C31" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="D31" s="2">
+        <v>110</v>
+      </c>
+      <c r="E31" s="11">
+        <v>28.42</v>
+      </c>
+      <c r="F31" s="11">
+        <v>81.3</v>
+      </c>
+      <c r="G31" s="10">
+        <f t="shared" si="2"/>
+        <v>14.498848397621895</v>
+      </c>
+      <c r="H31" s="10">
+        <f t="shared" si="3"/>
+        <v>1594.8733237384085</v>
+      </c>
       <c r="I31" s="10"/>
     </row>
-    <row r="32" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A32" s="10"/>
       <c r="B32" s="10"/>
-      <c r="C32" s="10"/>
-      <c r="D32" s="10"/>
-      <c r="E32" s="10"/>
-      <c r="F32" s="10"/>
-      <c r="G32" s="10"/>
-      <c r="H32" s="10"/>
+      <c r="C32" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="D32" s="2">
+        <v>70</v>
+      </c>
+      <c r="E32" s="11">
+        <v>29.76</v>
+      </c>
+      <c r="F32" s="11">
+        <v>95.38</v>
+      </c>
+      <c r="G32" s="10">
+        <f t="shared" si="2"/>
+        <v>12.787994049528825</v>
+      </c>
+      <c r="H32" s="10">
+        <f t="shared" si="3"/>
+        <v>895.1595834670178</v>
+      </c>
       <c r="I32" s="10"/>
     </row>
-    <row r="33" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A33" s="10"/>
       <c r="B33" s="10"/>
-      <c r="C33" s="10"/>
-      <c r="D33" s="10"/>
-      <c r="E33" s="10"/>
-      <c r="F33" s="10"/>
-      <c r="G33" s="10"/>
-      <c r="H33" s="10"/>
+      <c r="C33" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="D33" s="2">
+        <v>170</v>
+      </c>
+      <c r="E33" s="11">
+        <v>42.36</v>
+      </c>
+      <c r="F33" s="11">
+        <v>71.06</v>
+      </c>
+      <c r="G33" s="10">
+        <f t="shared" si="2"/>
+        <v>17.895852728423943</v>
+      </c>
+      <c r="H33" s="10">
+        <f t="shared" si="3"/>
+        <v>3042.2949638320702</v>
+      </c>
       <c r="I33" s="10"/>
     </row>
-    <row r="34" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A34" s="10"/>
       <c r="B34" s="10"/>
-      <c r="C34" s="10"/>
-      <c r="D34" s="10"/>
-      <c r="E34" s="10"/>
-      <c r="F34" s="10"/>
-      <c r="G34" s="10"/>
-      <c r="H34" s="10"/>
+      <c r="C34" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="D34" s="2">
+        <v>200</v>
+      </c>
+      <c r="E34" s="11">
+        <v>41.84</v>
+      </c>
+      <c r="F34" s="11">
+        <v>87.68</v>
+      </c>
+      <c r="G34" s="10">
+        <f t="shared" si="2"/>
+        <v>1.6078808113800336</v>
+      </c>
+      <c r="H34" s="10">
+        <f t="shared" si="3"/>
+        <v>321.5761622760067</v>
+      </c>
       <c r="I34" s="10"/>
     </row>
-    <row r="35" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A35" s="10"/>
       <c r="B35" s="10"/>
-      <c r="C35" s="10"/>
-      <c r="D35" s="10"/>
-      <c r="E35" s="10"/>
-      <c r="F35" s="10"/>
-      <c r="G35" s="10"/>
-      <c r="H35" s="10"/>
+      <c r="C35" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="D35" s="2">
+        <v>50</v>
+      </c>
+      <c r="E35" s="11">
+        <v>44.98</v>
+      </c>
+      <c r="F35" s="11">
+        <v>93.27</v>
+      </c>
+      <c r="G35" s="10">
+        <f t="shared" si="2"/>
+        <v>6.0741199295519461</v>
+      </c>
+      <c r="H35" s="10">
+        <f t="shared" si="3"/>
+        <v>303.7059964775973</v>
+      </c>
       <c r="I35" s="10"/>
     </row>
-    <row r="36" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A36" s="10"/>
       <c r="B36" s="10"/>
       <c r="C36" s="10"/>
@@ -1604,10 +1777,13 @@
       <c r="E36" s="10"/>
       <c r="F36" s="10"/>
       <c r="G36" s="10"/>
-      <c r="H36" s="10"/>
+      <c r="H36" s="10">
+        <f>SUM(H28:H35)</f>
+        <v>16276.588415497434</v>
+      </c>
       <c r="I36" s="10"/>
     </row>
-    <row r="37" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A37" s="10"/>
       <c r="B37" s="10"/>
       <c r="C37" s="10"/>
@@ -1618,18 +1794,24 @@
       <c r="H37" s="10"/>
       <c r="I37" s="10"/>
     </row>
-    <row r="38" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A38" s="10"/>
       <c r="B38" s="10"/>
-      <c r="C38" s="10"/>
+      <c r="C38" s="10" t="s">
+        <v>17</v>
+      </c>
       <c r="D38" s="10"/>
-      <c r="E38" s="10"/>
-      <c r="F38" s="10"/>
+      <c r="E38" s="10">
+        <v>40.776166537087448</v>
+      </c>
+      <c r="F38" s="10">
+        <v>88.885628079795595</v>
+      </c>
       <c r="G38" s="10"/>
       <c r="H38" s="10"/>
       <c r="I38" s="10"/>
     </row>
-    <row r="39" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A39" s="10"/>
       <c r="B39" s="10"/>
       <c r="C39" s="10"/>
@@ -1640,7 +1822,7 @@
       <c r="H39" s="10"/>
       <c r="I39" s="10"/>
     </row>
-    <row r="40" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A40" s="10"/>
       <c r="B40" s="10"/>
       <c r="C40" s="10"/>
@@ -1651,7 +1833,7 @@
       <c r="H40" s="10"/>
       <c r="I40" s="10"/>
     </row>
-    <row r="41" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A41" s="10"/>
       <c r="B41" s="10"/>
       <c r="C41" s="10"/>
@@ -1662,7 +1844,7 @@
       <c r="H41" s="10"/>
       <c r="I41" s="10"/>
     </row>
-    <row r="42" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A42" s="10"/>
       <c r="B42" s="10"/>
       <c r="C42" s="10"/>
@@ -1673,7 +1855,7 @@
       <c r="H42" s="10"/>
       <c r="I42" s="10"/>
     </row>
-    <row r="43" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A43" s="10"/>
       <c r="B43" s="10"/>
       <c r="C43" s="10"/>
@@ -1684,7 +1866,7 @@
       <c r="H43" s="10"/>
       <c r="I43" s="10"/>
     </row>
-    <row r="44" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A44" s="10"/>
       <c r="B44" s="10"/>
       <c r="C44" s="10"/>
@@ -1695,7 +1877,7 @@
       <c r="H44" s="10"/>
       <c r="I44" s="10"/>
     </row>
-    <row r="45" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A45" s="10"/>
       <c r="B45" s="10"/>
       <c r="C45" s="10"/>
@@ -1706,7 +1888,7 @@
       <c r="H45" s="10"/>
       <c r="I45" s="10"/>
     </row>
-    <row r="46" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A46" s="10"/>
       <c r="B46" s="10"/>
       <c r="C46" s="10"/>
@@ -1717,7 +1899,7 @@
       <c r="H46" s="10"/>
       <c r="I46" s="10"/>
     </row>
-    <row r="47" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A47" s="10"/>
       <c r="B47" s="10"/>
       <c r="C47" s="10"/>
@@ -1728,7 +1910,7 @@
       <c r="H47" s="10"/>
       <c r="I47" s="10"/>
     </row>
-    <row r="48" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A48" s="10"/>
       <c r="B48" s="10"/>
       <c r="C48" s="10"/>
@@ -1739,7 +1921,7 @@
       <c r="H48" s="10"/>
       <c r="I48" s="10"/>
     </row>
-    <row r="49" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A49" s="10"/>
       <c r="B49" s="10"/>
       <c r="C49" s="10"/>
@@ -1750,7 +1932,7 @@
       <c r="H49" s="10"/>
       <c r="I49" s="10"/>
     </row>
-    <row r="50" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A50" s="10"/>
       <c r="B50" s="10"/>
       <c r="C50" s="10"/>
@@ -1761,7 +1943,7 @@
       <c r="H50" s="10"/>
       <c r="I50" s="10"/>
     </row>
-    <row r="51" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A51" s="10"/>
       <c r="B51" s="10"/>
       <c r="C51" s="10"/>
@@ -1772,7 +1954,7 @@
       <c r="H51" s="10"/>
       <c r="I51" s="10"/>
     </row>
-    <row r="52" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A52" s="10"/>
       <c r="B52" s="10"/>
       <c r="C52" s="10"/>
@@ -1783,7 +1965,7 @@
       <c r="H52" s="10"/>
       <c r="I52" s="10"/>
     </row>
-    <row r="53" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A53" s="10"/>
       <c r="B53" s="10"/>
       <c r="C53" s="10"/>
@@ -1794,7 +1976,7 @@
       <c r="H53" s="10"/>
       <c r="I53" s="10"/>
     </row>
-    <row r="54" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A54" s="10"/>
       <c r="B54" s="10"/>
       <c r="C54" s="10"/>
@@ -1805,7 +1987,7 @@
       <c r="H54" s="10"/>
       <c r="I54" s="10"/>
     </row>
-    <row r="55" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A55" s="10"/>
       <c r="B55" s="10"/>
       <c r="C55" s="10"/>
@@ -1816,7 +1998,7 @@
       <c r="H55" s="10"/>
       <c r="I55" s="10"/>
     </row>
-    <row r="56" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A56" s="10"/>
       <c r="B56" s="10"/>
       <c r="C56" s="10"/>
@@ -1827,7 +2009,7 @@
       <c r="H56" s="10"/>
       <c r="I56" s="10"/>
     </row>
-    <row r="57" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A57" s="10"/>
       <c r="B57" s="10"/>
       <c r="C57" s="10"/>
@@ -1838,7 +2020,7 @@
       <c r="H57" s="10"/>
       <c r="I57" s="10"/>
     </row>
-    <row r="58" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A58" s="10"/>
       <c r="B58" s="10"/>
       <c r="C58" s="10"/>
@@ -1849,7 +2031,7 @@
       <c r="H58" s="10"/>
       <c r="I58" s="10"/>
     </row>
-    <row r="59" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A59" s="10"/>
       <c r="B59" s="10"/>
       <c r="C59" s="10"/>
@@ -1860,7 +2042,7 @@
       <c r="H59" s="10"/>
       <c r="I59" s="10"/>
     </row>
-    <row r="60" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A60" s="10"/>
       <c r="B60" s="10"/>
       <c r="C60" s="10"/>
@@ -1871,7 +2053,7 @@
       <c r="H60" s="10"/>
       <c r="I60" s="10"/>
     </row>
-    <row r="61" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A61" s="10"/>
       <c r="B61" s="10"/>
       <c r="C61" s="10"/>
@@ -1882,7 +2064,7 @@
       <c r="H61" s="10"/>
       <c r="I61" s="10"/>
     </row>
-    <row r="62" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A62" s="10"/>
       <c r="B62" s="10"/>
       <c r="C62" s="10"/>
@@ -1893,7 +2075,7 @@
       <c r="H62" s="10"/>
       <c r="I62" s="10"/>
     </row>
-    <row r="63" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A63" s="10"/>
       <c r="B63" s="10"/>
       <c r="C63" s="10"/>
@@ -1904,7 +2086,7 @@
       <c r="H63" s="10"/>
       <c r="I63" s="10"/>
     </row>
-    <row r="64" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A64" s="10"/>
       <c r="B64" s="10"/>
       <c r="C64" s="10"/>
@@ -1915,7 +2097,7 @@
       <c r="H64" s="10"/>
       <c r="I64" s="10"/>
     </row>
-    <row r="65" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A65" s="10"/>
       <c r="B65" s="10"/>
       <c r="C65" s="10"/>
@@ -1926,7 +2108,7 @@
       <c r="H65" s="10"/>
       <c r="I65" s="10"/>
     </row>
-    <row r="66" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A66" s="10"/>
       <c r="B66" s="10"/>
       <c r="C66" s="10"/>
@@ -1937,7 +2119,7 @@
       <c r="H66" s="10"/>
       <c r="I66" s="10"/>
     </row>
-    <row r="67" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="67" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A67" s="10"/>
       <c r="B67" s="10"/>
       <c r="C67" s="10"/>
@@ -1948,7 +2130,7 @@
       <c r="H67" s="10"/>
       <c r="I67" s="10"/>
     </row>
-    <row r="68" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A68" s="10"/>
       <c r="B68" s="10"/>
       <c r="C68" s="10"/>
@@ -1959,7 +2141,7 @@
       <c r="H68" s="10"/>
       <c r="I68" s="10"/>
     </row>
-    <row r="69" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="69" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A69" s="10"/>
       <c r="B69" s="10"/>
       <c r="C69" s="10"/>
@@ -1970,7 +2152,7 @@
       <c r="H69" s="10"/>
       <c r="I69" s="10"/>
     </row>
-    <row r="70" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="70" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A70" s="10"/>
       <c r="B70" s="10"/>
       <c r="C70" s="10"/>
@@ -1981,7 +2163,7 @@
       <c r="H70" s="10"/>
       <c r="I70" s="10"/>
     </row>
-    <row r="71" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="71" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A71" s="10"/>
       <c r="B71" s="10"/>
       <c r="C71" s="10"/>
@@ -1992,7 +2174,7 @@
       <c r="H71" s="10"/>
       <c r="I71" s="10"/>
     </row>
-    <row r="72" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="72" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A72" s="10"/>
       <c r="B72" s="10"/>
       <c r="C72" s="10"/>
@@ -2003,7 +2185,7 @@
       <c r="H72" s="10"/>
       <c r="I72" s="10"/>
     </row>
-    <row r="73" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="73" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A73" s="10"/>
       <c r="B73" s="10"/>
       <c r="C73" s="10"/>
@@ -2014,7 +2196,7 @@
       <c r="H73" s="10"/>
       <c r="I73" s="10"/>
     </row>
-    <row r="74" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="74" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A74" s="10"/>
       <c r="B74" s="10"/>
       <c r="C74" s="10"/>
@@ -2025,7 +2207,7 @@
       <c r="H74" s="10"/>
       <c r="I74" s="10"/>
     </row>
-    <row r="75" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="75" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A75" s="10"/>
       <c r="B75" s="10"/>
       <c r="C75" s="10"/>
@@ -2036,7 +2218,7 @@
       <c r="H75" s="10"/>
       <c r="I75" s="10"/>
     </row>
-    <row r="76" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="76" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A76" s="10"/>
       <c r="B76" s="10"/>
       <c r="C76" s="10"/>
@@ -2047,7 +2229,7 @@
       <c r="H76" s="10"/>
       <c r="I76" s="10"/>
     </row>
-    <row r="77" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="77" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A77" s="10"/>
       <c r="B77" s="10"/>
       <c r="C77" s="10"/>
@@ -2058,7 +2240,7 @@
       <c r="H77" s="10"/>
       <c r="I77" s="10"/>
     </row>
-    <row r="78" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="78" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A78" s="10"/>
       <c r="B78" s="10"/>
       <c r="C78" s="10"/>
@@ -2069,7 +2251,7 @@
       <c r="H78" s="10"/>
       <c r="I78" s="10"/>
     </row>
-    <row r="79" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="79" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A79" s="10"/>
       <c r="B79" s="10"/>
       <c r="C79" s="10"/>
@@ -2080,7 +2262,7 @@
       <c r="H79" s="10"/>
       <c r="I79" s="10"/>
     </row>
-    <row r="80" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="80" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A80" s="10"/>
       <c r="B80" s="10"/>
       <c r="C80" s="10"/>
@@ -2091,7 +2273,7 @@
       <c r="H80" s="10"/>
       <c r="I80" s="10"/>
     </row>
-    <row r="81" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="81" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A81" s="10"/>
       <c r="B81" s="10"/>
       <c r="C81" s="10"/>
@@ -2102,7 +2284,7 @@
       <c r="H81" s="10"/>
       <c r="I81" s="10"/>
     </row>
-    <row r="82" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="82" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A82" s="10"/>
       <c r="B82" s="10"/>
       <c r="C82" s="10"/>
@@ -2113,7 +2295,7 @@
       <c r="H82" s="10"/>
       <c r="I82" s="10"/>
     </row>
-    <row r="83" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="83" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A83" s="10"/>
       <c r="B83" s="10"/>
       <c r="C83" s="10"/>
@@ -2124,7 +2306,7 @@
       <c r="H83" s="10"/>
       <c r="I83" s="10"/>
     </row>
-    <row r="84" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="84" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A84" s="10"/>
       <c r="B84" s="10"/>
       <c r="C84" s="10"/>
@@ -2135,7 +2317,7 @@
       <c r="H84" s="10"/>
       <c r="I84" s="10"/>
     </row>
-    <row r="85" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="85" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A85" s="10"/>
       <c r="B85" s="10"/>
       <c r="C85" s="10"/>
@@ -2146,7 +2328,7 @@
       <c r="H85" s="10"/>
       <c r="I85" s="10"/>
     </row>
-    <row r="86" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="86" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A86" s="10"/>
       <c r="B86" s="10"/>
       <c r="C86" s="10"/>
@@ -2157,7 +2339,7 @@
       <c r="H86" s="10"/>
       <c r="I86" s="10"/>
     </row>
-    <row r="87" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="87" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A87" s="10"/>
       <c r="B87" s="10"/>
       <c r="C87" s="10"/>
@@ -2168,7 +2350,7 @@
       <c r="H87" s="10"/>
       <c r="I87" s="10"/>
     </row>
-    <row r="88" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="88" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A88" s="10"/>
       <c r="B88" s="10"/>
       <c r="C88" s="10"/>
@@ -2179,7 +2361,7 @@
       <c r="H88" s="10"/>
       <c r="I88" s="10"/>
     </row>
-    <row r="89" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="89" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A89" s="10"/>
       <c r="B89" s="10"/>
       <c r="C89" s="10"/>
@@ -2190,7 +2372,7 @@
       <c r="H89" s="10"/>
       <c r="I89" s="10"/>
     </row>
-    <row r="90" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="90" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A90" s="10"/>
       <c r="B90" s="10"/>
       <c r="C90" s="10"/>
@@ -2201,7 +2383,7 @@
       <c r="H90" s="10"/>
       <c r="I90" s="10"/>
     </row>
-    <row r="91" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="91" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A91" s="10"/>
       <c r="B91" s="10"/>
       <c r="C91" s="10"/>
@@ -2212,7 +2394,7 @@
       <c r="H91" s="10"/>
       <c r="I91" s="10"/>
     </row>
-    <row r="92" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="92" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A92" s="10"/>
       <c r="B92" s="10"/>
       <c r="C92" s="10"/>
@@ -2223,7 +2405,7 @@
       <c r="H92" s="10"/>
       <c r="I92" s="10"/>
     </row>
-    <row r="93" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="93" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A93" s="10"/>
       <c r="B93" s="10"/>
       <c r="C93" s="10"/>
@@ -2234,7 +2416,7 @@
       <c r="H93" s="10"/>
       <c r="I93" s="10"/>
     </row>
-    <row r="94" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="94" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A94" s="10"/>
       <c r="B94" s="10"/>
       <c r="C94" s="10"/>
@@ -2245,7 +2427,7 @@
       <c r="H94" s="10"/>
       <c r="I94" s="10"/>
     </row>
-    <row r="95" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="95" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A95" s="10"/>
       <c r="B95" s="10"/>
       <c r="C95" s="10"/>
@@ -2256,7 +2438,7 @@
       <c r="H95" s="10"/>
       <c r="I95" s="10"/>
     </row>
-    <row r="96" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="96" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A96" s="10"/>
       <c r="B96" s="10"/>
       <c r="C96" s="10"/>
@@ -2267,7 +2449,7 @@
       <c r="H96" s="10"/>
       <c r="I96" s="10"/>
     </row>
-    <row r="97" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="97" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A97" s="10"/>
       <c r="B97" s="10"/>
       <c r="C97" s="10"/>
@@ -2278,7 +2460,7 @@
       <c r="H97" s="10"/>
       <c r="I97" s="10"/>
     </row>
-    <row r="98" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="98" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A98" s="10"/>
       <c r="B98" s="10"/>
       <c r="C98" s="10"/>
@@ -2289,7 +2471,7 @@
       <c r="H98" s="10"/>
       <c r="I98" s="10"/>
     </row>
-    <row r="99" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="99" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A99" s="10"/>
       <c r="B99" s="10"/>
       <c r="C99" s="10"/>
@@ -2300,7 +2482,7 @@
       <c r="H99" s="10"/>
       <c r="I99" s="10"/>
     </row>
-    <row r="100" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="100" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A100" s="10"/>
       <c r="B100" s="10"/>
       <c r="C100" s="10"/>
@@ -2311,7 +2493,7 @@
       <c r="H100" s="10"/>
       <c r="I100" s="10"/>
     </row>
-    <row r="101" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="101" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A101" s="10"/>
       <c r="B101" s="10"/>
       <c r="C101" s="10"/>
@@ -2322,7 +2504,7 @@
       <c r="H101" s="10"/>
       <c r="I101" s="10"/>
     </row>
-    <row r="102" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="102" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A102" s="10"/>
       <c r="B102" s="10"/>
       <c r="C102" s="10"/>
@@ -2333,7 +2515,7 @@
       <c r="H102" s="10"/>
       <c r="I102" s="10"/>
     </row>
-    <row r="103" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="103" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A103" s="10"/>
       <c r="B103" s="10"/>
       <c r="C103" s="10"/>
@@ -2344,7 +2526,7 @@
       <c r="H103" s="10"/>
       <c r="I103" s="10"/>
     </row>
-    <row r="104" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="104" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A104" s="10"/>
       <c r="B104" s="10"/>
       <c r="C104" s="10"/>
@@ -2355,7 +2537,7 @@
       <c r="H104" s="10"/>
       <c r="I104" s="10"/>
     </row>
-    <row r="105" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="105" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A105" s="10"/>
       <c r="B105" s="10"/>
       <c r="C105" s="10"/>
@@ -2366,7 +2548,7 @@
       <c r="H105" s="10"/>
       <c r="I105" s="10"/>
     </row>
-    <row r="106" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="106" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A106" s="10"/>
       <c r="B106" s="10"/>
       <c r="C106" s="10"/>
@@ -2377,7 +2559,7 @@
       <c r="H106" s="10"/>
       <c r="I106" s="10"/>
     </row>
-    <row r="107" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="107" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A107" s="10"/>
       <c r="B107" s="10"/>
       <c r="C107" s="10"/>
@@ -2388,7 +2570,7 @@
       <c r="H107" s="10"/>
       <c r="I107" s="10"/>
     </row>
-    <row r="108" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="108" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A108" s="10"/>
       <c r="B108" s="10"/>
       <c r="C108" s="10"/>
@@ -2399,7 +2581,7 @@
       <c r="H108" s="10"/>
       <c r="I108" s="10"/>
     </row>
-    <row r="109" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="109" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A109" s="10"/>
       <c r="B109" s="10"/>
       <c r="C109" s="10"/>
@@ -2410,7 +2592,7 @@
       <c r="H109" s="10"/>
       <c r="I109" s="10"/>
     </row>
-    <row r="110" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="110" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A110" s="10"/>
       <c r="B110" s="10"/>
       <c r="C110" s="10"/>
@@ -2421,7 +2603,7 @@
       <c r="H110" s="10"/>
       <c r="I110" s="10"/>
     </row>
-    <row r="111" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="111" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A111" s="10"/>
       <c r="B111" s="10"/>
       <c r="C111" s="10"/>
@@ -2432,7 +2614,7 @@
       <c r="H111" s="10"/>
       <c r="I111" s="10"/>
     </row>
-    <row r="112" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="112" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A112" s="10"/>
       <c r="B112" s="10"/>
       <c r="C112" s="10"/>
@@ -2443,7 +2625,7 @@
       <c r="H112" s="10"/>
       <c r="I112" s="10"/>
     </row>
-    <row r="113" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="113" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A113" s="10"/>
       <c r="B113" s="10"/>
       <c r="C113" s="10"/>
@@ -2454,7 +2636,7 @@
       <c r="H113" s="10"/>
       <c r="I113" s="10"/>
     </row>
-    <row r="114" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="114" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A114" s="10"/>
       <c r="B114" s="10"/>
       <c r="C114" s="10"/>
@@ -2465,7 +2647,7 @@
       <c r="H114" s="10"/>
       <c r="I114" s="10"/>
     </row>
-    <row r="115" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="115" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A115" s="10"/>
       <c r="B115" s="10"/>
       <c r="C115" s="10"/>
@@ -2476,7 +2658,7 @@
       <c r="H115" s="10"/>
       <c r="I115" s="10"/>
     </row>
-    <row r="116" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="116" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A116" s="10"/>
       <c r="B116" s="10"/>
       <c r="C116" s="10"/>
@@ -2487,7 +2669,7 @@
       <c r="H116" s="10"/>
       <c r="I116" s="10"/>
     </row>
-    <row r="117" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="117" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A117" s="10"/>
       <c r="B117" s="10"/>
       <c r="C117" s="10"/>
@@ -2498,7 +2680,7 @@
       <c r="H117" s="10"/>
       <c r="I117" s="10"/>
     </row>
-    <row r="118" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="118" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A118" s="10"/>
       <c r="B118" s="10"/>
       <c r="C118" s="10"/>
@@ -2509,7 +2691,7 @@
       <c r="H118" s="10"/>
       <c r="I118" s="10"/>
     </row>
-    <row r="119" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="119" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A119" s="10"/>
       <c r="B119" s="10"/>
       <c r="C119" s="10"/>
@@ -2520,7 +2702,7 @@
       <c r="H119" s="10"/>
       <c r="I119" s="10"/>
     </row>
-    <row r="120" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="120" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A120" s="10"/>
       <c r="B120" s="10"/>
       <c r="C120" s="10"/>
@@ -2531,7 +2713,7 @@
       <c r="H120" s="10"/>
       <c r="I120" s="10"/>
     </row>
-    <row r="121" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="121" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A121" s="10"/>
       <c r="B121" s="10"/>
       <c r="C121" s="10"/>
@@ -2542,7 +2724,7 @@
       <c r="H121" s="10"/>
       <c r="I121" s="10"/>
     </row>
-    <row r="122" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="122" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A122" s="10"/>
       <c r="B122" s="10"/>
       <c r="C122" s="10"/>
@@ -2553,7 +2735,7 @@
       <c r="H122" s="10"/>
       <c r="I122" s="10"/>
     </row>
-    <row r="123" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="123" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A123" s="10"/>
       <c r="B123" s="10"/>
       <c r="C123" s="10"/>
@@ -2564,7 +2746,7 @@
       <c r="H123" s="10"/>
       <c r="I123" s="10"/>
     </row>
-    <row r="124" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="124" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A124" s="10"/>
       <c r="B124" s="10"/>
       <c r="C124" s="10"/>
@@ -2575,7 +2757,7 @@
       <c r="H124" s="10"/>
       <c r="I124" s="10"/>
     </row>
-    <row r="125" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="125" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A125" s="10"/>
       <c r="B125" s="10"/>
       <c r="C125" s="10"/>
@@ -2586,7 +2768,7 @@
       <c r="H125" s="10"/>
       <c r="I125" s="10"/>
     </row>
-    <row r="126" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="126" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A126" s="10"/>
       <c r="B126" s="10"/>
       <c r="C126" s="10"/>
@@ -2597,7 +2779,7 @@
       <c r="H126" s="10"/>
       <c r="I126" s="10"/>
     </row>
-    <row r="127" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="127" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A127" s="10"/>
       <c r="B127" s="10"/>
       <c r="C127" s="10"/>
@@ -2608,7 +2790,7 @@
       <c r="H127" s="10"/>
       <c r="I127" s="10"/>
     </row>
-    <row r="128" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="128" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A128" s="10"/>
       <c r="B128" s="10"/>
       <c r="C128" s="10"/>
@@ -2619,7 +2801,7 @@
       <c r="H128" s="10"/>
       <c r="I128" s="10"/>
     </row>
-    <row r="129" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="129" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A129" s="10"/>
       <c r="B129" s="10"/>
       <c r="C129" s="10"/>
@@ -2630,7 +2812,7 @@
       <c r="H129" s="10"/>
       <c r="I129" s="10"/>
     </row>
-    <row r="130" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="130" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A130" s="10"/>
       <c r="B130" s="10"/>
       <c r="C130" s="10"/>
@@ -2641,7 +2823,7 @@
       <c r="H130" s="10"/>
       <c r="I130" s="10"/>
     </row>
-    <row r="131" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="131" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A131" s="10"/>
       <c r="B131" s="10"/>
       <c r="C131" s="10"/>
@@ -2652,7 +2834,7 @@
       <c r="H131" s="10"/>
       <c r="I131" s="10"/>
     </row>
-    <row r="132" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="132" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A132" s="10"/>
       <c r="B132" s="10"/>
       <c r="C132" s="10"/>
@@ -2663,7 +2845,7 @@
       <c r="H132" s="10"/>
       <c r="I132" s="10"/>
     </row>
-    <row r="133" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="133" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A133" s="10"/>
       <c r="B133" s="10"/>
       <c r="C133" s="10"/>
@@ -2674,7 +2856,7 @@
       <c r="H133" s="10"/>
       <c r="I133" s="10"/>
     </row>
-    <row r="134" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="134" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A134" s="10"/>
       <c r="B134" s="10"/>
       <c r="C134" s="10"/>
@@ -2685,7 +2867,7 @@
       <c r="H134" s="10"/>
       <c r="I134" s="10"/>
     </row>
-    <row r="135" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="135" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A135" s="10"/>
       <c r="B135" s="10"/>
       <c r="C135" s="10"/>
@@ -2696,7 +2878,7 @@
       <c r="H135" s="10"/>
       <c r="I135" s="10"/>
     </row>
-    <row r="136" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="136" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A136" s="10"/>
       <c r="B136" s="10"/>
       <c r="C136" s="10"/>
@@ -2707,7 +2889,7 @@
       <c r="H136" s="10"/>
       <c r="I136" s="10"/>
     </row>
-    <row r="137" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="137" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A137" s="10"/>
       <c r="B137" s="10"/>
       <c r="C137" s="10"/>
@@ -2718,7 +2900,7 @@
       <c r="H137" s="10"/>
       <c r="I137" s="10"/>
     </row>
-    <row r="138" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="138" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A138" s="10"/>
       <c r="B138" s="10"/>
       <c r="C138" s="10"/>
@@ -2729,7 +2911,7 @@
       <c r="H138" s="10"/>
       <c r="I138" s="10"/>
     </row>
-    <row r="139" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="139" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A139" s="10"/>
       <c r="B139" s="10"/>
       <c r="C139" s="10"/>
@@ -2740,7 +2922,7 @@
       <c r="H139" s="10"/>
       <c r="I139" s="10"/>
     </row>
-    <row r="140" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="140" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A140" s="10"/>
       <c r="B140" s="10"/>
       <c r="C140" s="10"/>
@@ -2751,7 +2933,7 @@
       <c r="H140" s="10"/>
       <c r="I140" s="10"/>
     </row>
-    <row r="141" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="141" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A141" s="10"/>
       <c r="B141" s="10"/>
       <c r="C141" s="10"/>
@@ -2762,7 +2944,7 @@
       <c r="H141" s="10"/>
       <c r="I141" s="10"/>
     </row>
-    <row r="142" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="142" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A142" s="10"/>
       <c r="B142" s="10"/>
       <c r="C142" s="10"/>
@@ -2773,7 +2955,7 @@
       <c r="H142" s="10"/>
       <c r="I142" s="10"/>
     </row>
-    <row r="143" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="143" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A143" s="10"/>
       <c r="B143" s="10"/>
       <c r="C143" s="10"/>
@@ -2784,7 +2966,7 @@
       <c r="H143" s="10"/>
       <c r="I143" s="10"/>
     </row>
-    <row r="144" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="144" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A144" s="10"/>
       <c r="B144" s="10"/>
       <c r="C144" s="10"/>
@@ -2795,7 +2977,7 @@
       <c r="H144" s="10"/>
       <c r="I144" s="10"/>
     </row>
-    <row r="145" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="145" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A145" s="10"/>
       <c r="B145" s="10"/>
       <c r="C145" s="10"/>
@@ -2806,7 +2988,7 @@
       <c r="H145" s="10"/>
       <c r="I145" s="10"/>
     </row>
-    <row r="146" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="146" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A146" s="10"/>
       <c r="B146" s="10"/>
       <c r="C146" s="10"/>
@@ -2817,7 +2999,7 @@
       <c r="H146" s="10"/>
       <c r="I146" s="10"/>
     </row>
-    <row r="147" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="147" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A147" s="10"/>
       <c r="B147" s="10"/>
       <c r="C147" s="10"/>
@@ -2828,7 +3010,7 @@
       <c r="H147" s="10"/>
       <c r="I147" s="10"/>
     </row>
-    <row r="148" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="148" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A148" s="10"/>
       <c r="B148" s="10"/>
       <c r="C148" s="10"/>
@@ -2839,7 +3021,7 @@
       <c r="H148" s="10"/>
       <c r="I148" s="10"/>
     </row>
-    <row r="149" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="149" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A149" s="10"/>
       <c r="B149" s="10"/>
       <c r="C149" s="10"/>
@@ -2850,7 +3032,7 @@
       <c r="H149" s="10"/>
       <c r="I149" s="10"/>
     </row>
-    <row r="150" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="150" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A150" s="10"/>
       <c r="B150" s="10"/>
       <c r="C150" s="10"/>
@@ -2861,7 +3043,7 @@
       <c r="H150" s="10"/>
       <c r="I150" s="10"/>
     </row>
-    <row r="151" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="151" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A151" s="10"/>
       <c r="B151" s="10"/>
       <c r="C151" s="10"/>
@@ -2872,7 +3054,7 @@
       <c r="H151" s="10"/>
       <c r="I151" s="10"/>
     </row>
-    <row r="152" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="152" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A152" s="10"/>
       <c r="B152" s="10"/>
       <c r="C152" s="10"/>
@@ -2883,7 +3065,7 @@
       <c r="H152" s="10"/>
       <c r="I152" s="10"/>
     </row>
-    <row r="153" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="153" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A153" s="10"/>
       <c r="B153" s="10"/>
       <c r="C153" s="10"/>
@@ -2894,7 +3076,7 @@
       <c r="H153" s="10"/>
       <c r="I153" s="10"/>
     </row>
-    <row r="154" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="154" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A154" s="10"/>
       <c r="B154" s="10"/>
       <c r="C154" s="10"/>
@@ -2905,7 +3087,7 @@
       <c r="H154" s="10"/>
       <c r="I154" s="10"/>
     </row>
-    <row r="155" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="155" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A155" s="10"/>
       <c r="B155" s="10"/>
       <c r="C155" s="10"/>
@@ -2916,7 +3098,7 @@
       <c r="H155" s="10"/>
       <c r="I155" s="10"/>
     </row>
-    <row r="156" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="156" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A156" s="10"/>
       <c r="B156" s="10"/>
       <c r="C156" s="10"/>
@@ -2927,7 +3109,7 @@
       <c r="H156" s="10"/>
       <c r="I156" s="10"/>
     </row>
-    <row r="157" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="157" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A157" s="10"/>
       <c r="B157" s="10"/>
       <c r="C157" s="10"/>
@@ -2938,7 +3120,7 @@
       <c r="H157" s="10"/>
       <c r="I157" s="10"/>
     </row>
-    <row r="158" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="158" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A158" s="10"/>
       <c r="B158" s="10"/>
       <c r="C158" s="10"/>
@@ -2949,7 +3131,7 @@
       <c r="H158" s="10"/>
       <c r="I158" s="10"/>
     </row>
-    <row r="159" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="159" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A159" s="10"/>
       <c r="B159" s="10"/>
       <c r="C159" s="10"/>
@@ -2960,7 +3142,7 @@
       <c r="H159" s="10"/>
       <c r="I159" s="10"/>
     </row>
-    <row r="160" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="160" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A160" s="10"/>
       <c r="B160" s="10"/>
       <c r="C160" s="10"/>
@@ -2971,7 +3153,7 @@
       <c r="H160" s="10"/>
       <c r="I160" s="10"/>
     </row>
-    <row r="161" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="161" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A161" s="10"/>
       <c r="B161" s="10"/>
       <c r="C161" s="10"/>
@@ -2982,7 +3164,7 @@
       <c r="H161" s="10"/>
       <c r="I161" s="10"/>
     </row>
-    <row r="162" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="162" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A162" s="10"/>
       <c r="B162" s="10"/>
       <c r="C162" s="10"/>
@@ -2993,7 +3175,7 @@
       <c r="H162" s="10"/>
       <c r="I162" s="10"/>
     </row>
-    <row r="163" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="163" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A163" s="10"/>
       <c r="B163" s="10"/>
       <c r="C163" s="10"/>
@@ -3004,7 +3186,7 @@
       <c r="H163" s="10"/>
       <c r="I163" s="10"/>
     </row>
-    <row r="164" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="164" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A164" s="10"/>
       <c r="B164" s="10"/>
       <c r="C164" s="10"/>
@@ -3015,7 +3197,7 @@
       <c r="H164" s="10"/>
       <c r="I164" s="10"/>
     </row>
-    <row r="165" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="165" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A165" s="10"/>
       <c r="B165" s="10"/>
       <c r="C165" s="10"/>
@@ -3026,7 +3208,7 @@
       <c r="H165" s="10"/>
       <c r="I165" s="10"/>
     </row>
-    <row r="166" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="166" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A166" s="10"/>
       <c r="B166" s="10"/>
       <c r="C166" s="10"/>
@@ -3037,7 +3219,7 @@
       <c r="H166" s="10"/>
       <c r="I166" s="10"/>
     </row>
-    <row r="167" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="167" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A167" s="10"/>
       <c r="B167" s="10"/>
       <c r="C167" s="10"/>
@@ -3048,7 +3230,7 @@
       <c r="H167" s="10"/>
       <c r="I167" s="10"/>
     </row>
-    <row r="168" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="168" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A168" s="10"/>
       <c r="B168" s="10"/>
       <c r="C168" s="10"/>
@@ -3059,7 +3241,7 @@
       <c r="H168" s="10"/>
       <c r="I168" s="10"/>
     </row>
-    <row r="169" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="169" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A169" s="10"/>
       <c r="B169" s="10"/>
       <c r="C169" s="10"/>
@@ -3070,7 +3252,7 @@
       <c r="H169" s="10"/>
       <c r="I169" s="10"/>
     </row>
-    <row r="170" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="170" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A170" s="10"/>
       <c r="B170" s="10"/>
       <c r="C170" s="10"/>
@@ -3081,7 +3263,7 @@
       <c r="H170" s="10"/>
       <c r="I170" s="10"/>
     </row>
-    <row r="171" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="171" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A171" s="10"/>
       <c r="B171" s="10"/>
       <c r="C171" s="10"/>
@@ -3092,7 +3274,7 @@
       <c r="H171" s="10"/>
       <c r="I171" s="10"/>
     </row>
-    <row r="172" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="172" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A172" s="10"/>
       <c r="B172" s="10"/>
       <c r="C172" s="10"/>
@@ -3103,7 +3285,7 @@
       <c r="H172" s="10"/>
       <c r="I172" s="10"/>
     </row>
-    <row r="173" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="173" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A173" s="10"/>
       <c r="B173" s="10"/>
       <c r="C173" s="10"/>
@@ -3132,7 +3314,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <extLst>
@@ -3146,7 +3328,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <extLst>
@@ -3160,7 +3342,7 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{008BAF6A-9496-D145-A308-373519879514}">
   <dimension ref="A1"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="11.5546875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -3169,7 +3351,7 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CA15A333-C5F5-1E4A-BD78-AE5542BFF1D1}">
   <dimension ref="A1"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="11.5546875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -3178,17 +3360,17 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{50AF00E3-AAEF-734A-93AE-FC7F9B54D08E}">
   <dimension ref="A198:D208"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="10.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="16384" width="10.83203125" style="10"/>
+    <col min="1" max="16384" width="10.77734375" style="10"/>
   </cols>
   <sheetData>
-    <row r="198" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="198" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A198" s="12" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="200" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="200" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A200" s="10" t="s">
         <v>12</v>
       </c>
@@ -3202,7 +3384,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="201" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="201" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A201" s="7" t="s">
         <v>0</v>
       </c>
@@ -3216,7 +3398,7 @@
         <v>122.33</v>
       </c>
     </row>
-    <row r="202" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="202" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A202" s="7" t="s">
         <v>1</v>
       </c>
@@ -3230,7 +3412,7 @@
         <v>122.42</v>
       </c>
     </row>
-    <row r="203" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="203" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A203" s="7" t="s">
         <v>2</v>
       </c>
@@ -3244,7 +3426,7 @@
         <v>117.16</v>
       </c>
     </row>
-    <row r="204" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="204" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A204" s="7" t="s">
         <v>3</v>
       </c>
@@ -3258,7 +3440,7 @@
         <v>81.3</v>
       </c>
     </row>
-    <row r="205" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="205" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A205" s="7" t="s">
         <v>4</v>
       </c>
@@ -3272,7 +3454,7 @@
         <v>95.38</v>
       </c>
     </row>
-    <row r="206" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="206" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A206" s="7" t="s">
         <v>5</v>
       </c>
@@ -3286,7 +3468,7 @@
         <v>71.06</v>
       </c>
     </row>
-    <row r="207" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="207" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A207" s="7" t="s">
         <v>6</v>
       </c>
@@ -3300,7 +3482,7 @@
         <v>87.68</v>
       </c>
     </row>
-    <row r="208" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="208" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A208" s="7" t="s">
         <v>7</v>
       </c>
